--- a/backend/samples/sample_aaos_test_cases.xlsx
+++ b/backend/samples/sample_aaos_test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\sources\Simple\backend\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4956715D-6E28-47FA-BE07-A4C82F91F974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65994B93-DCDF-4C8E-B25C-4872263DD2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{82FFD9A1-7183-46E0-9367-B65192E0D42B}"/>
   </bookViews>
@@ -535,64 +535,64 @@
     <t>REQ_CON_069</t>
   </si>
   <si>
-    <t>TC_SMP_BT_120</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_130</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_111</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_112</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_113</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_114</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_115</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_116</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_117</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_118</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_119</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_121</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_122</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_123</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_124</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_125</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_126</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_127</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_128</t>
-  </si>
-  <si>
-    <t>TC_SMP_BT_129</t>
+    <t>TC_SMP_BT_1112</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1113</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1114</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1115</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1116</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1117</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1118</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1119</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1120</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1121</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1122</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1123</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1124</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1125</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1126</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1127</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1128</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1129</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1130</t>
+  </si>
+  <si>
+    <t>TC_SMP_BT_1131</t>
   </si>
 </sst>
 </file>
@@ -1488,7 +1488,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -1529,7 +1529,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B4" t="s">
         <v>35</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B5" t="s">
         <v>44</v>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
         <v>51</v>
@@ -1693,7 +1693,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B8" t="s">
         <v>67</v>
@@ -1775,7 +1775,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s">
         <v>76</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B10" t="s">
         <v>83</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="B11" t="s">
         <v>91</v>
@@ -1898,7 +1898,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B12" t="s">
         <v>98</v>
@@ -1939,7 +1939,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B13" t="s">
         <v>107</v>
@@ -1980,7 +1980,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B14" t="s">
         <v>113</v>
@@ -2021,7 +2021,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B15" t="s">
         <v>120</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s">
         <v>127</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s">
         <v>135</v>
@@ -2144,7 +2144,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s">
         <v>142</v>
@@ -2185,7 +2185,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B19" t="s">
         <v>150</v>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B20" t="s">
         <v>158</v>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="B21" t="s">
         <v>165</v>
